--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261019.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>557,552,668</t>
+          <t>11,793,967</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>11,793,967</t>
+          <t>557,552,668</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2,237,752</t>
+          <t>7,378,900</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,378,900</t>
+          <t>2,237,752</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>18,799,773</t>
+          <t>8,286,606</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,286,606</t>
+          <t>18,799,773</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>256,315,151</t>
+          <t>27,229,620</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>27,229,620</t>
+          <t>256,315,151</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
